--- a/Example/Excel/Test.xlsx
+++ b/Example/Excel/Test.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE4810A-9F7E-4FC2-81A7-9EF3FDBAA0EF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC624722-3DAC-4D8D-93AF-FC81C37EB5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="45" windowWidth="28710" windowHeight="15210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TestSheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
